--- a/Result/profitability/6517.xlsx
+++ b/Result/profitability/6517.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5260,6 +5260,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6517</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>113</v>
+      </c>
+      <c r="D39" t="n">
+        <v>69</v>
+      </c>
+      <c r="E39" t="n">
+        <v>44</v>
+      </c>
+      <c r="F39" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="G39" t="n">
+        <v>18</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>16.27%</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>21</v>
+      </c>
+      <c r="K39" t="n">
+        <v>18</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.55375</v>
+      </c>
+      <c r="N39" t="n">
+        <v>37.21749999999999</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.1678216330219946</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-2.017241379310345</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.960000000000001</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.05326086956521747</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
